--- a/template/7.7/净值.xlsx
+++ b/template/7.7/净值.xlsx
@@ -1070,7 +1070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="11" min="1" max="1"/>
@@ -3229,18 +3229,202 @@
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="0" t="n">
         <v>0.99758</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>-0.2458%</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.99298</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>-0.7055%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>-0.2458%</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.99298</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>-0.7055%</t>
         </is>
@@ -3258,7 +3442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -5415,18 +5599,202 @@
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="0" t="n">
         <v>0.99642</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>-0.3618%</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.99182</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>-0.8216%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>-0.3618%</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.99182</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>-0.8216%</t>
         </is>
@@ -5444,7 +5812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -7212,18 +7580,202 @@
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="0" t="n">
         <v>0.98304</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>-4.008%</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0.98233</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>-4.0561%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.98304</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-4.008%</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>-4.0561%</t>
         </is>
@@ -7240,7 +7792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -9008,18 +9560,202 @@
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="0" t="n">
         <v>1.00315</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>-2.4484%</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>1.00244</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>-2.496%</t>
         </is>
@@ -9037,7 +9773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -9563,18 +10299,202 @@
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>0.99588</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>-0.4913%</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.99382</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.6863%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.99588</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-0.4913%</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.99382</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>-0.6863%</t>
         </is>
@@ -9591,7 +10511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -10118,18 +11038,202 @@
           <t>2025/07/07</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>1.00007</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>-0.0733%</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.998</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>-0.2683%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.00007</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-0.0733%</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>-0.2683%</t>
         </is>

--- a/template/7.7/净值.xlsx
+++ b/template/7.7/净值.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9060" tabRatio="600" firstSheet="1" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="14175" tabRatio="600" firstSheet="1" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00000_ "/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy\/mm\/dd"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="168" formatCode="yyyy\/mm\/dd"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -637,7 +638,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -655,6 +656,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -664,7 +666,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -685,14 +687,15 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1071,15 +1074,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E102"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="11" min="1" max="1"/>
-    <col width="16.3796296296296" customWidth="1" style="13" min="2" max="2"/>
-    <col width="15.25" customWidth="1" style="14" min="3" max="3"/>
-    <col width="19.6666666666667" customWidth="1" style="15" min="4" max="4"/>
-    <col width="19.5555555555556" customWidth="1" style="16" min="5" max="5"/>
-    <col width="9" customWidth="1" style="5" min="6" max="16379"/>
-    <col width="9" customWidth="1" style="5" min="16380" max="16384"/>
+    <col width="11.6333333333333" customWidth="1" style="12" min="1" max="1"/>
+    <col width="16.3833333333333" customWidth="1" style="14" min="2" max="2"/>
+    <col width="15.25" customWidth="1" style="15" min="3" max="3"/>
+    <col width="19.6666666666667" customWidth="1" style="16" min="4" max="4"/>
+    <col width="19.5583333333333" customWidth="1" style="17" min="5" max="5"/>
+    <col width="9" customWidth="1" style="5" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1088,7 +1090,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -1098,7 +1100,7 @@
           <t>回撤-有返息</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-无返息</t>
         </is>
@@ -1110,28 +1112,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="n">
+      <c r="A2" s="18" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="n">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -1144,17 +1146,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -1167,17 +1169,17 @@
           <t>-0.002%</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>0.99998</v>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>-0.002%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -1190,17 +1192,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -1213,17 +1215,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>1.00004</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -1236,17 +1238,17 @@
           <t>-0.048%</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>0.99956</v>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -1259,17 +1261,17 @@
           <t>-0.048%</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>0.99956</v>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -1282,17 +1284,17 @@
           <t>-0.048%</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>0.99956</v>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -1305,17 +1307,17 @@
           <t>-0.018%</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>0.99986</v>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>-0.018%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -1328,17 +1330,17 @@
           <t>-0.046%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.99958</v>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>-0.046%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -1351,17 +1353,17 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>0.99984</v>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -1374,17 +1376,17 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.99984</v>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -1397,17 +1399,17 @@
           <t>-0.064%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9994</v>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>-0.064%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -1420,17 +1422,17 @@
           <t>-0.066%</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.99938</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>-0.066%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -1443,17 +1445,17 @@
           <t>-0.099%</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.99905</v>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>-0.099%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -1466,17 +1468,17 @@
           <t>-0.233%</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.99771</v>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>-0.233%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -1489,17 +1491,17 @@
           <t>-0.229%</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.99775</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>-0.229%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -1512,17 +1514,17 @@
           <t>-0.228%</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>0.99776</v>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>-0.228%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -1535,17 +1537,17 @@
           <t>-0.224%</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>0.9978</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>-0.224%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -1558,17 +1560,17 @@
           <t>-0.216%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>0.99788</v>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>-0.216%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -1581,17 +1583,17 @@
           <t>-0.206%</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <v>0.99798</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>-0.206%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -1604,17 +1606,17 @@
           <t>-0.7645%</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
         <v>0.997870438666667</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>-0.2458%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -1627,17 +1629,17 @@
           <t>-0.2458%</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
         <v>0.997800438666667</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>-0.7645%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -1650,17 +1652,17 @@
           <t>-0.194%</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
         <v>0.997910438666667</v>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>-0.2129%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -1673,17 +1675,17 @@
           <t>-0.191%</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
         <v>0.997940438666667</v>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>-0.2099%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -1696,17 +1698,17 @@
           <t>-0.179%</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>0.998060438666667</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>-0.1979%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -1719,17 +1721,17 @@
           <t>-0.175%</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <v>0.998100438666667</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>-0.1939%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -1742,17 +1744,17 @@
           <t>-0.131%</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="16" t="n">
         <v>0.998540438666667</v>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>-0.15%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -1765,17 +1767,17 @@
           <t>-0.126%</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="16" t="n">
         <v>0.998590438666667</v>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>-0.145%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -1788,17 +1790,17 @@
           <t>-0.091%</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="16" t="n">
         <v>0.998940438666667</v>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>-0.11%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -1811,17 +1813,17 @@
           <t>-0.481%</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="16" t="n">
         <v>0.995040438666667</v>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>-0.4999%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -1834,17 +1836,17 @@
           <t>-0.417%</t>
         </is>
       </c>
-      <c r="D33" s="15" t="n">
+      <c r="D33" s="16" t="n">
         <v>0.995680438666667</v>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>-0.4359%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -1857,17 +1859,17 @@
           <t>-0.415%</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="16" t="n">
         <v>0.995700438666667</v>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>-0.4339%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -1880,17 +1882,17 @@
           <t>-0.411%</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
         <v>0.9957404386666669</v>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>-0.4299%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -1903,17 +1905,17 @@
           <t>-0.377%</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>0.996080438666667</v>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>-0.3959%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -1926,17 +1928,17 @@
           <t>-0.129%</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>0.998560438666667</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>-0.148%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -1949,17 +1951,17 @@
           <t>-0.124%</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="16" t="n">
         <v>0.998610438666667</v>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>-0.143%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -1972,17 +1974,17 @@
           <t>-0.115%</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
+      <c r="D39" s="16" t="n">
         <v>0.998700438666667</v>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>-0.134%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -1995,17 +1997,17 @@
           <t>-0.178%</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="16" t="n">
         <v>0.998070438666667</v>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>-0.1969%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -2018,17 +2020,17 @@
           <t>-0.281%</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="16" t="n">
         <v>0.997040438666667</v>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>-0.2999%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -2041,17 +2043,17 @@
           <t>-0.262%</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="16" t="n">
         <v>0.9972304386666671</v>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>-0.2809%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -2064,17 +2066,17 @@
           <t>-0.257%</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="16" t="n">
         <v>0.997280438666667</v>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>-0.2759%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -2087,17 +2089,17 @@
           <t>-0.22%</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="16" t="n">
         <v>0.997650438666667</v>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>-0.2389%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -2110,17 +2112,17 @@
           <t>-0.345%</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="16" t="n">
         <v>0.9964004386666671</v>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>-0.3639%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -2133,17 +2135,17 @@
           <t>-0.437%</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="16" t="n">
         <v>0.995480438666667</v>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>-0.4559%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -2156,17 +2158,17 @@
           <t>-0.585%</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
         <v>0.994000438666667</v>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>-0.6039%</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -2179,17 +2181,17 @@
           <t>-0.573%</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="16" t="n">
         <v>0.994105484333333</v>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>-0.5934%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -2202,17 +2204,17 @@
           <t>-0.527%</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="16" t="n">
         <v>0.994565484333333</v>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>-0.5474%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -2225,17 +2227,17 @@
           <t>-0.417%</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="16" t="n">
         <v>0.995665484333333</v>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>-0.4374%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -2248,17 +2250,17 @@
           <t>-0.325%</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="16" t="n">
         <v>0.996585484333333</v>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>-0.3454%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -2271,17 +2273,17 @@
           <t>-0.272%</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="16" t="n">
         <v>0.997115484333333</v>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>-0.2924%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -2294,17 +2296,17 @@
           <t>-0.326%</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="16" t="n">
         <v>0.996575484333333</v>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>-0.3464%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -2317,17 +2319,17 @@
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="16" t="n">
         <v>0.996835484333333</v>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>-0.3204%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -2340,17 +2342,17 @@
           <t>-0.286%</t>
         </is>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D55" s="16" t="n">
         <v>0.9969754843333331</v>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>-0.3064%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -2363,17 +2365,17 @@
           <t>-0.287%</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
         <v>0.996965484333333</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>-0.3074%</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -2386,17 +2388,17 @@
           <t>-0.283%</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
         <v>0.997005484333333</v>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>-0.3034%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -2409,17 +2411,17 @@
           <t>-0.274%</t>
         </is>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D58" s="16" t="n">
         <v>0.9970954843333329</v>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>-0.2944%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -2432,17 +2434,17 @@
           <t>-0.257%</t>
         </is>
       </c>
-      <c r="D59" s="15" t="n">
+      <c r="D59" s="16" t="n">
         <v>0.997265484333333</v>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>-0.2774%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -2455,17 +2457,17 @@
           <t>-0.239%</t>
         </is>
       </c>
-      <c r="D60" s="15" t="n">
+      <c r="D60" s="16" t="n">
         <v>0.997445484333333</v>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>-0.2594%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -2478,17 +2480,17 @@
           <t>-0.243%</t>
         </is>
       </c>
-      <c r="D61" s="15" t="n">
+      <c r="D61" s="16" t="n">
         <v>0.997405484333333</v>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>-0.2634%</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -2501,17 +2503,17 @@
           <t>-0.278%</t>
         </is>
       </c>
-      <c r="D62" s="15" t="n">
+      <c r="D62" s="16" t="n">
         <v>0.997055484333333</v>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>-0.2984%</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -2524,17 +2526,17 @@
           <t>-0.406%</t>
         </is>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="16" t="n">
         <v>0.995775484333333</v>
       </c>
-      <c r="E63" s="16" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>-0.4264%</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -2547,17 +2549,17 @@
           <t>-0.384%</t>
         </is>
       </c>
-      <c r="D64" s="15" t="n">
+      <c r="D64" s="16" t="n">
         <v>0.995995484333333</v>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>-0.4044%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -2570,17 +2572,17 @@
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="D65" s="15" t="n">
+      <c r="D65" s="16" t="n">
         <v>0.996335484333333</v>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>-0.3704%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -2593,17 +2595,17 @@
           <t>-0.336%</t>
         </is>
       </c>
-      <c r="D66" s="15" t="n">
+      <c r="D66" s="16" t="n">
         <v>0.996475484333333</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>-0.3564%</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -2616,17 +2618,17 @@
           <t>-0.343%</t>
         </is>
       </c>
-      <c r="D67" s="15" t="n">
+      <c r="D67" s="16" t="n">
         <v>0.996399997</v>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>-0.364%</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -2639,17 +2641,17 @@
           <t>-0.375%</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D68" s="16" t="n">
         <v>0.9960799970000001</v>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>-0.396%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -2662,17 +2664,17 @@
           <t>-0.344%</t>
         </is>
       </c>
-      <c r="D69" s="15" t="n">
+      <c r="D69" s="16" t="n">
         <v>0.996389997</v>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>-0.365%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -2685,17 +2687,17 @@
           <t>-0.374%</t>
         </is>
       </c>
-      <c r="D70" s="15" t="n">
+      <c r="D70" s="16" t="n">
         <v>0.996089997</v>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>-0.395%</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -2708,17 +2710,17 @@
           <t>-0.355%</t>
         </is>
       </c>
-      <c r="D71" s="15" t="n">
+      <c r="D71" s="16" t="n">
         <v>0.996279997</v>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>-0.376%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -2731,17 +2733,17 @@
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
+      <c r="D72" s="16" t="n">
         <v>0.996329997</v>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>-0.371%</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -2754,17 +2756,17 @@
           <t>-0.358%</t>
         </is>
       </c>
-      <c r="D73" s="15" t="n">
+      <c r="D73" s="16" t="n">
         <v>0.9962499970000001</v>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>-0.379%</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -2777,17 +2779,17 @@
           <t>-0.325%</t>
         </is>
       </c>
-      <c r="D74" s="15" t="n">
+      <c r="D74" s="16" t="n">
         <v>0.996579997</v>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>-0.346%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -2800,17 +2802,17 @@
           <t>-0.312%</t>
         </is>
       </c>
-      <c r="D75" s="15" t="n">
+      <c r="D75" s="16" t="n">
         <v>0.996709997</v>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>-0.333%</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="18" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -2823,17 +2825,17 @@
           <t>-0.302%</t>
         </is>
       </c>
-      <c r="D76" s="15" t="n">
+      <c r="D76" s="16" t="n">
         <v>0.9968099969999999</v>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>-0.323%</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -2846,17 +2848,17 @@
           <t>-0.291%</t>
         </is>
       </c>
-      <c r="D77" s="15" t="n">
+      <c r="D77" s="16" t="n">
         <v>0.996919997</v>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>-0.312%</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="18" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -2869,17 +2871,17 @@
           <t>-0.281%</t>
         </is>
       </c>
-      <c r="D78" s="15" t="n">
+      <c r="D78" s="16" t="n">
         <v>0.997019997</v>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="E78" s="17" t="inlineStr">
         <is>
           <t>-0.302%</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -2892,17 +2894,17 @@
           <t>-0.274%</t>
         </is>
       </c>
-      <c r="D79" s="15" t="n">
+      <c r="D79" s="16" t="n">
         <v>0.997089997</v>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E79" s="17" t="inlineStr">
         <is>
           <t>-0.295%</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="18" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -2915,17 +2917,17 @@
           <t>-0.265%</t>
         </is>
       </c>
-      <c r="D80" s="15" t="n">
+      <c r="D80" s="16" t="n">
         <v>0.997179997</v>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E80" s="17" t="inlineStr">
         <is>
           <t>-0.286%</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -2938,17 +2940,17 @@
           <t>-0.269%</t>
         </is>
       </c>
-      <c r="D81" s="15" t="n">
+      <c r="D81" s="16" t="n">
         <v>0.997139997</v>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E81" s="17" t="inlineStr">
         <is>
           <t>-0.29%</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -2961,17 +2963,17 @@
           <t>-0.345%</t>
         </is>
       </c>
-      <c r="D82" s="15" t="n">
+      <c r="D82" s="16" t="n">
         <v>0.996379997</v>
       </c>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="E82" s="17" t="inlineStr">
         <is>
           <t>-0.366%</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="inlineStr">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -2984,17 +2986,17 @@
           <t>-0.388%</t>
         </is>
       </c>
-      <c r="D83" s="15" t="n">
+      <c r="D83" s="16" t="n">
         <v>0.995949997</v>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E83" s="17" t="inlineStr">
         <is>
           <t>-0.409%</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="18" t="inlineStr">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -3007,17 +3009,17 @@
           <t>-0.31%</t>
         </is>
       </c>
-      <c r="D84" s="15" t="n">
+      <c r="D84" s="16" t="n">
         <v>0.9960491299999999</v>
       </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="E84" s="17" t="inlineStr">
         <is>
           <t>-0.3991%</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -3030,17 +3032,17 @@
           <t>-0.306%</t>
         </is>
       </c>
-      <c r="D85" s="15" t="n">
+      <c r="D85" s="16" t="n">
         <v>0.99608913</v>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="17" t="inlineStr">
         <is>
           <t>-0.3951%</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -3053,17 +3055,17 @@
           <t>-0.301%</t>
         </is>
       </c>
-      <c r="D86" s="15" t="n">
+      <c r="D86" s="16" t="n">
         <v>0.99613913</v>
       </c>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
         <is>
           <t>-0.3901%</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="18" t="inlineStr">
+      <c r="A87" s="19" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -3076,17 +3078,17 @@
           <t>-0.288%</t>
         </is>
       </c>
-      <c r="D87" s="15" t="n">
+      <c r="D87" s="16" t="n">
         <v>0.996254942333333</v>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="17" t="inlineStr">
         <is>
           <t>-0.3785%</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="18" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -3099,17 +3101,17 @@
           <t>-0.281%</t>
         </is>
       </c>
-      <c r="D88" s="15" t="n">
+      <c r="D88" s="16" t="n">
         <v>0.996324942333333</v>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E88" s="17" t="inlineStr">
         <is>
           <t>-0.3715%</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="inlineStr">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -3122,17 +3124,17 @@
           <t>-0.271%</t>
         </is>
       </c>
-      <c r="D89" s="15" t="n">
+      <c r="D89" s="16" t="n">
         <v>0.996424942333333</v>
       </c>
-      <c r="E89" s="16" t="inlineStr">
+      <c r="E89" s="17" t="inlineStr">
         <is>
           <t>-0.3615%</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="inlineStr">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -3145,17 +3147,17 @@
           <t>-0.277%</t>
         </is>
       </c>
-      <c r="D90" s="15" t="n">
+      <c r="D90" s="16" t="n">
         <v>0.9963649423333329</v>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E90" s="17" t="inlineStr">
         <is>
           <t>-0.3675%</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="inlineStr">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -3168,17 +3170,17 @@
           <t>-0.259%</t>
         </is>
       </c>
-      <c r="D91" s="15" t="n">
+      <c r="D91" s="16" t="n">
         <v>0.996544942333333</v>
       </c>
-      <c r="E91" s="16" t="inlineStr">
+      <c r="E91" s="17" t="inlineStr">
         <is>
           <t>-0.3495%</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
+      <c r="A92" s="19" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -3191,17 +3193,17 @@
           <t>-0.25%</t>
         </is>
       </c>
-      <c r="D92" s="15" t="n">
+      <c r="D92" s="16" t="n">
         <v>0.9966349423333331</v>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="17" t="inlineStr">
         <is>
           <t>-0.3405%</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="20" t="inlineStr">
+      <c r="A93" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3224,7 +3226,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="20" t="inlineStr">
+      <c r="A94" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3247,7 +3249,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="20" t="inlineStr">
+      <c r="A95" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3270,7 +3272,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="20" t="inlineStr">
+      <c r="A96" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3293,7 +3295,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="inlineStr">
+      <c r="A97" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3316,7 +3318,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
+      <c r="A98" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -3339,96 +3341,32 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="n">
-        <v>0.99758</v>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>-0.2458%</t>
-        </is>
-      </c>
-      <c r="D99" s="0" t="n">
-        <v>0.99298</v>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>-0.7055%</t>
-        </is>
-      </c>
+      <c r="A99" s="22" t="n"/>
+      <c r="B99" s="0" t="n"/>
+      <c r="C99" s="0" t="n"/>
+      <c r="D99" s="0" t="n"/>
+      <c r="E99" s="0" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B100" s="0" t="n">
-        <v>0.99758</v>
-      </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>-0.2458%</t>
-        </is>
-      </c>
-      <c r="D100" s="0" t="n">
-        <v>0.99298</v>
-      </c>
-      <c r="E100" s="0" t="inlineStr">
-        <is>
-          <t>-0.7055%</t>
-        </is>
-      </c>
+      <c r="A100" s="22" t="n"/>
+      <c r="B100" s="0" t="n"/>
+      <c r="C100" s="0" t="n"/>
+      <c r="D100" s="0" t="n"/>
+      <c r="E100" s="0" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B101" s="0" t="n">
-        <v>0.99758</v>
-      </c>
-      <c r="C101" s="0" t="inlineStr">
-        <is>
-          <t>-0.2458%</t>
-        </is>
-      </c>
-      <c r="D101" s="0" t="n">
-        <v>0.99298</v>
-      </c>
-      <c r="E101" s="0" t="inlineStr">
-        <is>
-          <t>-0.7055%</t>
-        </is>
-      </c>
+      <c r="A101" s="22" t="n"/>
+      <c r="B101" s="0" t="n"/>
+      <c r="C101" s="0" t="n"/>
+      <c r="D101" s="0" t="n"/>
+      <c r="E101" s="0" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0.99758</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>-0.2458%</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>0.99298</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-0.7055%</t>
-        </is>
-      </c>
+      <c r="A102" s="22" t="n"/>
+      <c r="B102" s="0" t="n"/>
+      <c r="C102" s="0" t="n"/>
+      <c r="D102" s="0" t="n"/>
+      <c r="E102" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3443,13 +3381,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E102"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="9.66666666666667" customWidth="1" style="15" min="2" max="2"/>
-    <col width="10.7777777777778" customWidth="1" style="16" min="3" max="3"/>
-    <col width="19.6666666666667" customWidth="1" style="15" min="4" max="4"/>
-    <col width="19.5555555555556" customWidth="1" style="16" min="5" max="5"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="9.66666666666667" customWidth="1" style="16" min="2" max="2"/>
+    <col width="10.775" customWidth="1" style="17" min="3" max="3"/>
+    <col width="19.6666666666667" customWidth="1" style="16" min="4" max="4"/>
+    <col width="19.5583333333333" customWidth="1" style="17" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3458,7 +3396,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -3468,7 +3406,7 @@
           <t>回撤-有返息</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-无返息</t>
         </is>
@@ -3480,28 +3418,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="n">
+      <c r="A2" s="18" t="n">
         <v>45709</v>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="n">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>2025/02/24</t>
         </is>
@@ -3514,17 +3452,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2025/02/25</t>
         </is>
@@ -3537,17 +3475,17 @@
           <t>-0.002%</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>0.99998</v>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>-0.002%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2025/02/26</t>
         </is>
@@ -3560,17 +3498,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2025/02/27</t>
         </is>
@@ -3583,17 +3521,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>1.00004</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2025/02/28</t>
         </is>
@@ -3606,17 +3544,17 @@
           <t>-0.048%</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>0.99956</v>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2025/03/03</t>
         </is>
@@ -3629,17 +3567,17 @@
           <t>-0.048%</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>0.99956</v>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2025/03/04</t>
         </is>
@@ -3652,17 +3590,17 @@
           <t>-0.048%</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>0.99956</v>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>-0.048%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>2025/03/05</t>
         </is>
@@ -3675,17 +3613,17 @@
           <t>-0.018%</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>0.99986</v>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>-0.018%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>2025/03/06</t>
         </is>
@@ -3698,17 +3636,17 @@
           <t>-0.046%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.99958</v>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>-0.046%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2025/03/07</t>
         </is>
@@ -3721,17 +3659,17 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>0.99984</v>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2025/03/10</t>
         </is>
@@ -3744,17 +3682,17 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.99984</v>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>-0.02%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2025/03/11</t>
         </is>
@@ -3767,17 +3705,17 @@
           <t>-0.064%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9994</v>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>-0.064%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2025/03/12</t>
         </is>
@@ -3790,17 +3728,17 @@
           <t>-0.066%</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.99938</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>-0.066%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2025/03/13</t>
         </is>
@@ -3813,17 +3751,17 @@
           <t>-0.099%</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.99905</v>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>-0.099%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2025/03/14</t>
         </is>
@@ -3836,17 +3774,17 @@
           <t>-0.233%</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.99771</v>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>-0.233%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>2025/03/17</t>
         </is>
@@ -3859,17 +3797,17 @@
           <t>-0.229%</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.99775</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>-0.229%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
@@ -3882,17 +3820,17 @@
           <t>-0.228%</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>0.99776</v>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>-0.228%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
@@ -3905,17 +3843,17 @@
           <t>-0.224%</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>0.9978</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>-0.224%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -3928,17 +3866,17 @@
           <t>-0.216%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>0.99788</v>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>-0.216%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -3951,17 +3889,17 @@
           <t>-0.206%</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <v>0.99798</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>-0.206%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -3974,17 +3912,17 @@
           <t>-0.198%</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
         <v>0.997870438666667</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>-0.2169%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -3997,17 +3935,17 @@
           <t>-0.205%</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
         <v>0.997800438666667</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>-0.2239%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -4020,17 +3958,17 @@
           <t>-0.194%</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
         <v>0.997910438666667</v>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>-0.2129%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -4043,17 +3981,17 @@
           <t>-0.191%</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
         <v>0.997940438666667</v>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>-0.2099%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -4066,17 +4004,17 @@
           <t>-0.179%</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>0.998060438666667</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>-0.1979%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -4089,17 +4027,17 @@
           <t>-0.175%</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <v>0.998100438666667</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>-0.1939%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -4112,17 +4050,17 @@
           <t>-0.131%</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="16" t="n">
         <v>0.998540438666667</v>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>-0.15%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -4135,17 +4073,17 @@
           <t>-0.126%</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="16" t="n">
         <v>0.998590438666667</v>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>-0.145%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -4158,17 +4096,17 @@
           <t>-0.091%</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="16" t="n">
         <v>0.998940438666667</v>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>-0.11%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -4181,17 +4119,17 @@
           <t>-0.481%</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="16" t="n">
         <v>0.995040438666667</v>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>-0.4999%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -4204,17 +4142,17 @@
           <t>-0.417%</t>
         </is>
       </c>
-      <c r="D33" s="15" t="n">
+      <c r="D33" s="16" t="n">
         <v>0.995680438666667</v>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>-0.4359%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -4227,17 +4165,17 @@
           <t>-0.391%</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="16" t="n">
         <v>0.995940438666667</v>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>-0.4099%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -4250,17 +4188,17 @@
           <t>-0.387%</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
         <v>0.995980438666667</v>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>-0.4059%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -4273,17 +4211,17 @@
           <t>-0.354%</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>0.996310438666667</v>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>-0.3729%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -4296,17 +4234,17 @@
           <t>-0.107%</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>0.998780438666667</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>-0.126%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -4319,17 +4257,17 @@
           <t>-0.105%</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="16" t="n">
         <v>0.998800438666667</v>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>-0.124%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -4342,17 +4280,17 @@
           <t>-0.096%</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
+      <c r="D39" s="16" t="n">
         <v>0.998890438666667</v>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>-0.115%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -4365,17 +4303,17 @@
           <t>-0.159%</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="16" t="n">
         <v>0.998260438666667</v>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>-0.1779%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -4388,17 +4326,17 @@
           <t>-0.262%</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="16" t="n">
         <v>0.9972304386666671</v>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>-0.2809%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -4411,17 +4349,17 @@
           <t>-0.243%</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="16" t="n">
         <v>0.997420438666667</v>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>-0.2619%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -4434,17 +4372,17 @@
           <t>-0.238%</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="16" t="n">
         <v>0.997470438666667</v>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>-0.2569%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -4457,17 +4395,17 @@
           <t>-0.201%</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="16" t="n">
         <v>0.9978404386666671</v>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>-0.2199%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -4480,17 +4418,17 @@
           <t>-0.324%</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="16" t="n">
         <v>0.996610438666667</v>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>-0.3429%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -4503,17 +4441,17 @@
           <t>-0.419%</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="16" t="n">
         <v>0.995660438666667</v>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>-0.4379%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -4526,17 +4464,17 @@
           <t>-0.566%</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
         <v>0.994190438666667</v>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>-0.5849%</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -4549,17 +4487,17 @@
           <t>-0.553%</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="16" t="n">
         <v>0.994305484333333</v>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>-0.5734%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -4572,17 +4510,17 @@
           <t>-0.527%</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="16" t="n">
         <v>0.994565484333333</v>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>-0.5474%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -4595,17 +4533,17 @@
           <t>-0.417%</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="16" t="n">
         <v>0.995665484333333</v>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>-0.4374%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -4618,17 +4556,17 @@
           <t>-0.325%</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="16" t="n">
         <v>0.996585484333333</v>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>-0.3454%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -4641,17 +4579,17 @@
           <t>-0.272%</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="16" t="n">
         <v>0.997115484333333</v>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>-0.2924%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -4664,17 +4602,17 @@
           <t>-0.326%</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="16" t="n">
         <v>0.996575484333333</v>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>-0.3464%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -4687,17 +4625,17 @@
           <t>-0.3%</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="16" t="n">
         <v>0.996835484333333</v>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>-0.3204%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -4710,17 +4648,17 @@
           <t>-0.286%</t>
         </is>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D55" s="16" t="n">
         <v>0.9969754843333331</v>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>-0.3064%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -4733,17 +4671,17 @@
           <t>-0.287%</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
         <v>0.996965484333333</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>-0.3074%</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -4756,17 +4694,17 @@
           <t>-0.283%</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
         <v>0.997005484333333</v>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>-0.3034%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -4779,17 +4717,17 @@
           <t>-0.274%</t>
         </is>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D58" s="16" t="n">
         <v>0.9970954843333329</v>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>-0.2944%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -4802,17 +4740,17 @@
           <t>-0.257%</t>
         </is>
       </c>
-      <c r="D59" s="15" t="n">
+      <c r="D59" s="16" t="n">
         <v>0.997265484333333</v>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>-0.2774%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -4825,17 +4763,17 @@
           <t>-0.239%</t>
         </is>
       </c>
-      <c r="D60" s="15" t="n">
+      <c r="D60" s="16" t="n">
         <v>0.997445484333333</v>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>-0.2594%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -4848,17 +4786,17 @@
           <t>-0.243%</t>
         </is>
       </c>
-      <c r="D61" s="15" t="n">
+      <c r="D61" s="16" t="n">
         <v>0.997405484333333</v>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>-0.2634%</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -4871,17 +4809,17 @@
           <t>-0.278%</t>
         </is>
       </c>
-      <c r="D62" s="15" t="n">
+      <c r="D62" s="16" t="n">
         <v>0.997055484333333</v>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>-0.2984%</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -4894,17 +4832,17 @@
           <t>-0.406%</t>
         </is>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="16" t="n">
         <v>0.995775484333333</v>
       </c>
-      <c r="E63" s="16" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>-0.4264%</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -4917,17 +4855,17 @@
           <t>-0.384%</t>
         </is>
       </c>
-      <c r="D64" s="15" t="n">
+      <c r="D64" s="16" t="n">
         <v>0.995995484333333</v>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>-0.4044%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -4940,17 +4878,17 @@
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="D65" s="15" t="n">
+      <c r="D65" s="16" t="n">
         <v>0.996335484333333</v>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>-0.3704%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -4963,17 +4901,17 @@
           <t>-0.336%</t>
         </is>
       </c>
-      <c r="D66" s="15" t="n">
+      <c r="D66" s="16" t="n">
         <v>0.996475484333333</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>-0.3564%</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -4986,17 +4924,17 @@
           <t>-0.343%</t>
         </is>
       </c>
-      <c r="D67" s="15" t="n">
+      <c r="D67" s="16" t="n">
         <v>0.996399997</v>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>-0.364%</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -5009,17 +4947,17 @@
           <t>-0.375%</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D68" s="16" t="n">
         <v>0.9960799970000001</v>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>-0.396%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -5032,17 +4970,17 @@
           <t>-0.344%</t>
         </is>
       </c>
-      <c r="D69" s="15" t="n">
+      <c r="D69" s="16" t="n">
         <v>0.996389997</v>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>-0.365%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -5055,17 +4993,17 @@
           <t>-0.374%</t>
         </is>
       </c>
-      <c r="D70" s="15" t="n">
+      <c r="D70" s="16" t="n">
         <v>0.996089997</v>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>-0.395%</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -5078,17 +5016,17 @@
           <t>-0.361%</t>
         </is>
       </c>
-      <c r="D71" s="15" t="n">
+      <c r="D71" s="16" t="n">
         <v>0.996219997</v>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>-0.382%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -5101,17 +5039,17 @@
           <t>-0.35%</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
+      <c r="D72" s="16" t="n">
         <v>0.996329997</v>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>-0.371%</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -5124,17 +5062,17 @@
           <t>-0.352%</t>
         </is>
       </c>
-      <c r="D73" s="15" t="n">
+      <c r="D73" s="16" t="n">
         <v>0.996309997</v>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>-0.373%</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -5147,17 +5085,17 @@
           <t>-0.325%</t>
         </is>
       </c>
-      <c r="D74" s="15" t="n">
+      <c r="D74" s="16" t="n">
         <v>0.996579997</v>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>-0.346%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -5170,17 +5108,17 @@
           <t>-0.312%</t>
         </is>
       </c>
-      <c r="D75" s="15" t="n">
+      <c r="D75" s="16" t="n">
         <v>0.996709997</v>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>-0.333%</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="18" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -5193,17 +5131,17 @@
           <t>-0.302%</t>
         </is>
       </c>
-      <c r="D76" s="15" t="n">
+      <c r="D76" s="16" t="n">
         <v>0.9968099969999999</v>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>-0.323%</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -5216,17 +5154,17 @@
           <t>-0.292%</t>
         </is>
       </c>
-      <c r="D77" s="15" t="n">
+      <c r="D77" s="16" t="n">
         <v>0.996909997</v>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>-0.313%</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="18" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -5239,17 +5177,17 @@
           <t>-0.281%</t>
         </is>
       </c>
-      <c r="D78" s="15" t="n">
+      <c r="D78" s="16" t="n">
         <v>0.997019997</v>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="E78" s="17" t="inlineStr">
         <is>
           <t>-0.302%</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -5262,17 +5200,17 @@
           <t>-0.274%</t>
         </is>
       </c>
-      <c r="D79" s="15" t="n">
+      <c r="D79" s="16" t="n">
         <v>0.997089997</v>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E79" s="17" t="inlineStr">
         <is>
           <t>-0.295%</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="18" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -5285,17 +5223,17 @@
           <t>-0.267%</t>
         </is>
       </c>
-      <c r="D80" s="15" t="n">
+      <c r="D80" s="16" t="n">
         <v>0.997159997</v>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E80" s="17" t="inlineStr">
         <is>
           <t>-0.288%</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -5308,17 +5246,17 @@
           <t>-0.269%</t>
         </is>
       </c>
-      <c r="D81" s="15" t="n">
+      <c r="D81" s="16" t="n">
         <v>0.997139997</v>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E81" s="17" t="inlineStr">
         <is>
           <t>-0.29%</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -5331,17 +5269,17 @@
           <t>-0.345%</t>
         </is>
       </c>
-      <c r="D82" s="15" t="n">
+      <c r="D82" s="16" t="n">
         <v>0.996379997</v>
       </c>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="E82" s="17" t="inlineStr">
         <is>
           <t>-0.366%</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="inlineStr">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -5354,17 +5292,17 @@
           <t>-0.388%</t>
         </is>
       </c>
-      <c r="D83" s="15" t="n">
+      <c r="D83" s="16" t="n">
         <v>0.995949997</v>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E83" s="17" t="inlineStr">
         <is>
           <t>-0.409%</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="18" t="inlineStr">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -5377,17 +5315,17 @@
           <t>-0.31%</t>
         </is>
       </c>
-      <c r="D84" s="15" t="n">
+      <c r="D84" s="16" t="n">
         <v>0.9960491299999999</v>
       </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="E84" s="17" t="inlineStr">
         <is>
           <t>-0.3991%</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -5400,17 +5338,17 @@
           <t>-0.306%</t>
         </is>
       </c>
-      <c r="D85" s="15" t="n">
+      <c r="D85" s="16" t="n">
         <v>0.99608913</v>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="17" t="inlineStr">
         <is>
           <t>-0.3951%</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -5423,17 +5361,17 @@
           <t>-0.301%</t>
         </is>
       </c>
-      <c r="D86" s="15" t="n">
+      <c r="D86" s="16" t="n">
         <v>0.99613913</v>
       </c>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
         <is>
           <t>-0.3901%</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="18" t="inlineStr">
+      <c r="A87" s="19" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -5446,17 +5384,17 @@
           <t>-0.288%</t>
         </is>
       </c>
-      <c r="D87" s="15" t="n">
+      <c r="D87" s="16" t="n">
         <v>0.996254942333333</v>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="17" t="inlineStr">
         <is>
           <t>-0.3785%</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="18" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -5469,17 +5407,17 @@
           <t>-0.281%</t>
         </is>
       </c>
-      <c r="D88" s="15" t="n">
+      <c r="D88" s="16" t="n">
         <v>0.996324942333333</v>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E88" s="17" t="inlineStr">
         <is>
           <t>-0.3715%</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="inlineStr">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -5492,17 +5430,17 @@
           <t>-0.271%</t>
         </is>
       </c>
-      <c r="D89" s="15" t="n">
+      <c r="D89" s="16" t="n">
         <v>0.996424942333333</v>
       </c>
-      <c r="E89" s="16" t="inlineStr">
+      <c r="E89" s="17" t="inlineStr">
         <is>
           <t>-0.3615%</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="inlineStr">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -5515,17 +5453,17 @@
           <t>-0.277%</t>
         </is>
       </c>
-      <c r="D90" s="15" t="n">
+      <c r="D90" s="16" t="n">
         <v>0.9963649423333329</v>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E90" s="17" t="inlineStr">
         <is>
           <t>-0.3675%</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="inlineStr">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -5538,17 +5476,17 @@
           <t>-0.259%</t>
         </is>
       </c>
-      <c r="D91" s="15" t="n">
+      <c r="D91" s="16" t="n">
         <v>0.996544942333333</v>
       </c>
-      <c r="E91" s="16" t="inlineStr">
+      <c r="E91" s="17" t="inlineStr">
         <is>
           <t>-0.3495%</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
+      <c r="A92" s="19" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -5561,17 +5499,17 @@
           <t>-0.25%</t>
         </is>
       </c>
-      <c r="D92" s="15" t="n">
+      <c r="D92" s="16" t="n">
         <v>0.9966349423333331</v>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="17" t="inlineStr">
         <is>
           <t>-0.3405%</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="20" t="inlineStr">
+      <c r="A93" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -5594,7 +5532,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="20" t="inlineStr">
+      <c r="A94" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -5617,7 +5555,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="20" t="inlineStr">
+      <c r="A95" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -5640,7 +5578,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="20" t="inlineStr">
+      <c r="A96" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -5663,7 +5601,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="inlineStr">
+      <c r="A97" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -5686,7 +5624,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
+      <c r="A98" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -5709,96 +5647,32 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="n">
-        <v>0.99642</v>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>-0.3618%</t>
-        </is>
-      </c>
-      <c r="D99" s="0" t="n">
-        <v>0.99182</v>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>-0.8216%</t>
-        </is>
-      </c>
+      <c r="A99" s="22" t="n"/>
+      <c r="B99" s="0" t="n"/>
+      <c r="C99" s="0" t="n"/>
+      <c r="D99" s="0" t="n"/>
+      <c r="E99" s="0" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B100" s="0" t="n">
-        <v>0.99642</v>
-      </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>-0.3618%</t>
-        </is>
-      </c>
-      <c r="D100" s="0" t="n">
-        <v>0.99182</v>
-      </c>
-      <c r="E100" s="0" t="inlineStr">
-        <is>
-          <t>-0.8216%</t>
-        </is>
-      </c>
+      <c r="A100" s="22" t="n"/>
+      <c r="B100" s="0" t="n"/>
+      <c r="C100" s="0" t="n"/>
+      <c r="D100" s="0" t="n"/>
+      <c r="E100" s="0" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B101" s="0" t="n">
-        <v>0.99642</v>
-      </c>
-      <c r="C101" s="0" t="inlineStr">
-        <is>
-          <t>-0.3618%</t>
-        </is>
-      </c>
-      <c r="D101" s="0" t="n">
-        <v>0.99182</v>
-      </c>
-      <c r="E101" s="0" t="inlineStr">
-        <is>
-          <t>-0.8216%</t>
-        </is>
-      </c>
+      <c r="A101" s="22" t="n"/>
+      <c r="B101" s="0" t="n"/>
+      <c r="C101" s="0" t="n"/>
+      <c r="D101" s="0" t="n"/>
+      <c r="E101" s="0" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0.99642</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>-0.3618%</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>0.99182</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-0.8216%</t>
-        </is>
-      </c>
+      <c r="A102" s="22" t="n"/>
+      <c r="B102" s="0" t="n"/>
+      <c r="C102" s="0" t="n"/>
+      <c r="D102" s="0" t="n"/>
+      <c r="E102" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5813,12 +5687,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16.5555555555556" customWidth="1" style="15" min="2" max="2"/>
-    <col width="17.3333333333333" customWidth="1" style="16" min="3" max="3"/>
-    <col width="18.5555555555556" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16.5583333333333" customWidth="1" style="16" min="2" max="2"/>
+    <col width="17.3333333333333" customWidth="1" style="17" min="3" max="3"/>
+    <col width="18.5583333333333" customWidth="1" style="1" min="4" max="4"/>
     <col width="18.3333333333333" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -5828,7 +5702,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -5838,7 +5712,7 @@
           <t>回撤-有返息</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-无返息</t>
         </is>
@@ -5850,53 +5724,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="n">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="n">
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -5919,7 +5793,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -5932,7 +5806,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>1.00006</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -5942,7 +5816,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -5965,7 +5839,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -5988,7 +5862,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -6011,7 +5885,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -6034,7 +5908,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -6057,7 +5931,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -6070,17 +5944,17 @@
           <t>-1.7014%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.994701667</v>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>-2.0547%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -6093,17 +5967,17 @@
           <t>-0.502%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>0.994931667</v>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>-0.5128%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -6116,17 +5990,17 @@
           <t>-0.463%</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.995321667</v>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>-0.4738%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -6139,17 +6013,17 @@
           <t>-0.781%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9921416669999999</v>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>-0.7918%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -6162,17 +6036,17 @@
           <t>-0.105%</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.998901667</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>-0.1158%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -6185,7 +6059,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>1.000771667</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -6195,7 +6069,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -6208,7 +6082,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>1.003731667</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -6218,7 +6092,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -6231,7 +6105,7 @@
           <t>-0.0976%</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>1.002751667</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -6241,7 +6115,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -6254,7 +6128,7 @@
           <t>-0.0249%</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="20" t="n">
         <v>1.003481667</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -6264,7 +6138,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -6277,17 +6151,17 @@
           <t>-0.0508%</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>1.003221667</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>-0.0259%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -6300,17 +6174,17 @@
           <t>-0.251%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>1.001211667</v>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>-0.2262%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -6323,17 +6197,17 @@
           <t>-0.4074%</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <v>0.999641667</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>-0.3827%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -6346,17 +6220,17 @@
           <t>-0.4602%</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
         <v>0.999111667</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>-0.4355%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -6369,17 +6243,17 @@
           <t>-0.3267%</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
         <v>1.000451667</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>-0.3019%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -6392,17 +6266,17 @@
           <t>-0.3228%</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
         <v>1.000491667</v>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>-0.298%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -6415,17 +6289,17 @@
           <t>-0.2869%</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
         <v>1.000851667</v>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>-0.2621%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -6438,17 +6312,17 @@
           <t>-0.4025%</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>0.999691667</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>-0.3777%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -6461,17 +6335,17 @@
           <t>-0.1833%</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <v>1.001891667</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>-0.1584%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -6484,7 +6358,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="20" t="n">
         <v>1.004461667</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -6494,7 +6368,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -6507,7 +6381,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="16" t="n">
         <v>1.004831667</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
@@ -6517,7 +6391,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -6530,7 +6404,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="16" t="n">
         <v>1.005851667</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
@@ -6540,7 +6414,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -6553,7 +6427,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="16" t="n">
         <v>1.008071667</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
@@ -6563,7 +6437,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -6576,7 +6450,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="20" t="n">
         <v>1.009051667</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
@@ -6586,7 +6460,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -6599,17 +6473,17 @@
           <t>-0.0466%</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="16" t="n">
         <v>1.008581667</v>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>-0.0466%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -6622,17 +6496,17 @@
           <t>-0.1407%</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
         <v>1.007631667</v>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>-0.1407%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -6645,17 +6519,17 @@
           <t>-0.1516%</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>1.007521667</v>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>-0.1516%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -6668,7 +6542,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>1.013381079</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
@@ -6678,7 +6552,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -6691,7 +6565,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="16" t="n">
         <v>1.015442585</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
@@ -6701,7 +6575,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -6714,7 +6588,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="20" t="n">
         <v>1.023862515</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
@@ -6724,7 +6598,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -6737,17 +6611,17 @@
           <t>-0.0547%</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="16" t="n">
         <v>1.023300992</v>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>-0.0548%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -6760,17 +6634,17 @@
           <t>-0.5273%</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="16" t="n">
         <v>1.018396345</v>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>-0.5339%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -6783,17 +6657,17 @@
           <t>-0.7656%</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="16" t="n">
         <v>1.015956345</v>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>-0.7722%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -6806,17 +6680,17 @@
           <t>-0.6972%</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="16" t="n">
         <v>1.016656345</v>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>-0.7038%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -6829,17 +6703,17 @@
           <t>-0.4961%</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="16" t="n">
         <v>1.018716345</v>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>-0.5026%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -6852,17 +6726,17 @@
           <t>-0.914%</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="16" t="n">
         <v>1.014436345</v>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>-0.9206%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -6875,17 +6749,17 @@
           <t>-1.412%</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="16" t="n">
         <v>1.009336345</v>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>-1.4188%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -6898,17 +6772,17 @@
           <t>-1.5311%</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
         <v>1.008116345</v>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>-1.5379%</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -6921,17 +6795,17 @@
           <t>-1.7655%</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="16" t="n">
         <v>1.005716345</v>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>-1.7723%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -6944,17 +6818,17 @@
           <t>-1.744%</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="16" t="n">
         <v>1.005935749</v>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>-1.7509%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -6967,17 +6841,17 @@
           <t>-1.4257%</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="16" t="n">
         <v>1.009195749</v>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>-1.4325%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -6990,17 +6864,17 @@
           <t>-2.0926%</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="16" t="n">
         <v>1.002365749</v>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>-2.0996%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -7013,17 +6887,17 @@
           <t>-2.2244%</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="16" t="n">
         <v>1.001015749</v>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>-2.2314%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -7036,17 +6910,17 @@
           <t>-2.6814%</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="16" t="n">
         <v>0.996335749</v>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>-2.6885%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -7059,17 +6933,17 @@
           <t>-2.7791%</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="16" t="n">
         <v>0.995335749</v>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>-2.7862%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -7082,17 +6956,17 @@
           <t>-2.9568%</t>
         </is>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D55" s="16" t="n">
         <v>0.9935157489999999</v>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>-2.9639%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -7105,17 +6979,17 @@
           <t>-3.03%</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
         <v>0.992730275</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>-3.0407%</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -7128,17 +7002,17 @@
           <t>-3.0281%</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
         <v>0.992708346</v>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>-3.0428%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -7151,17 +7025,17 @@
           <t>-2.9148%</t>
         </is>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D58" s="16" t="n">
         <v>0.993867209</v>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>-2.9296%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -7174,17 +7048,17 @@
           <t>-2.9099%</t>
         </is>
       </c>
-      <c r="D59" s="15" t="n">
+      <c r="D59" s="16" t="n">
         <v>0.993917117</v>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>-2.9247%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -7197,17 +7071,17 @@
           <t>-3.1237%</t>
         </is>
       </c>
-      <c r="D60" s="15" t="n">
+      <c r="D60" s="16" t="n">
         <v>0.991663972</v>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>-3.1448%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -7220,17 +7094,17 @@
           <t>-2.7732%</t>
         </is>
       </c>
-      <c r="D61" s="15" t="n">
+      <c r="D61" s="16" t="n">
         <v>0.995253972</v>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>-2.7942%</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -7243,17 +7117,17 @@
           <t>-2.7293%</t>
         </is>
       </c>
-      <c r="D62" s="15" t="n">
+      <c r="D62" s="16" t="n">
         <v>0.995703972</v>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>-2.7502%</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -7266,17 +7140,17 @@
           <t>-2.6716%</t>
         </is>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="16" t="n">
         <v>0.996293972</v>
       </c>
-      <c r="E63" s="16" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>-2.6926%</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -7289,17 +7163,17 @@
           <t>-3.0827%</t>
         </is>
       </c>
-      <c r="D64" s="15" t="n">
+      <c r="D64" s="16" t="n">
         <v>0.992083972</v>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>-3.1038%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -7312,17 +7186,17 @@
           <t>-3.0447%</t>
         </is>
       </c>
-      <c r="D65" s="15" t="n">
+      <c r="D65" s="16" t="n">
         <v>0.992473972</v>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>-3.0657%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -7335,17 +7209,17 @@
           <t>-3.1325%</t>
         </is>
       </c>
-      <c r="D66" s="15" t="n">
+      <c r="D66" s="16" t="n">
         <v>0.991573972</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>-3.1536%</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -7358,17 +7232,17 @@
           <t>-3.8122%</t>
         </is>
       </c>
-      <c r="D67" s="15" t="n">
+      <c r="D67" s="16" t="n">
         <v>0.984613972</v>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>-3.8334%</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -7381,17 +7255,17 @@
           <t>-3.818%</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D68" s="16" t="n">
         <v>0.984549702</v>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>-3.8397%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -7404,17 +7278,17 @@
           <t>-3.7204%</t>
         </is>
       </c>
-      <c r="D69" s="15" t="n">
+      <c r="D69" s="16" t="n">
         <v>0.985549702</v>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>-3.742%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -7427,17 +7301,17 @@
           <t>-3.696%</t>
         </is>
       </c>
-      <c r="D70" s="15" t="n">
+      <c r="D70" s="16" t="n">
         <v>0.985799702</v>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>-3.7176%</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -7450,17 +7324,17 @@
           <t>-3.3112%</t>
         </is>
       </c>
-      <c r="D71" s="15" t="n">
+      <c r="D71" s="16" t="n">
         <v>0.986700281</v>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>-3.6296%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -7473,17 +7347,17 @@
           <t>-3.571%</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
+      <c r="D72" s="16" t="n">
         <v>0.984040281</v>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>-3.8894%</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -7496,17 +7370,17 @@
           <t>-4.1852%</t>
         </is>
       </c>
-      <c r="D73" s="15" t="n">
+      <c r="D73" s="16" t="n">
         <v>0.9777502810000001</v>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>-4.5038%</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -7519,17 +7393,17 @@
           <t>-4.0592%</t>
         </is>
       </c>
-      <c r="D74" s="15" t="n">
+      <c r="D74" s="16" t="n">
         <v>0.979040281</v>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>-4.3778%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -7542,17 +7416,17 @@
           <t>-4.0045%</t>
         </is>
       </c>
-      <c r="D75" s="15" t="n">
+      <c r="D75" s="16" t="n">
         <v>0.979600281</v>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>-4.3231%</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="20" t="inlineStr">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -7562,7 +7436,7 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>-3.9867%</t>
+          <t>-4.008%</t>
         </is>
       </c>
       <c r="D76" s="0" t="n">
@@ -7570,12 +7444,12 @@
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>-4.0774%</t>
+          <t>-4.0561%</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+      <c r="A77" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -7598,7 +7472,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+      <c r="A78" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -7621,7 +7495,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -7644,7 +7518,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="20" t="inlineStr">
+      <c r="A80" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -7667,7 +7541,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="inlineStr">
+      <c r="A81" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -7690,96 +7564,32 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="n">
-        <v>0.98304</v>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t>-4.008%</t>
-        </is>
-      </c>
-      <c r="D82" s="0" t="n">
-        <v>0.98233</v>
-      </c>
-      <c r="E82" s="0" t="inlineStr">
-        <is>
-          <t>-4.0561%</t>
-        </is>
-      </c>
+      <c r="A82" s="22" t="n"/>
+      <c r="B82" s="0" t="n"/>
+      <c r="C82" s="0" t="n"/>
+      <c r="D82" s="0" t="n"/>
+      <c r="E82" s="0" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="n">
-        <v>0.98304</v>
-      </c>
-      <c r="C83" s="0" t="inlineStr">
-        <is>
-          <t>-4.008%</t>
-        </is>
-      </c>
-      <c r="D83" s="0" t="n">
-        <v>0.98233</v>
-      </c>
-      <c r="E83" s="0" t="inlineStr">
-        <is>
-          <t>-4.0561%</t>
-        </is>
-      </c>
+      <c r="A83" s="22" t="n"/>
+      <c r="B83" s="0" t="n"/>
+      <c r="C83" s="0" t="n"/>
+      <c r="D83" s="0" t="n"/>
+      <c r="E83" s="0" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="n">
-        <v>0.98304</v>
-      </c>
-      <c r="C84" s="0" t="inlineStr">
-        <is>
-          <t>-4.008%</t>
-        </is>
-      </c>
-      <c r="D84" s="0" t="n">
-        <v>0.98233</v>
-      </c>
-      <c r="E84" s="0" t="inlineStr">
-        <is>
-          <t>-4.0561%</t>
-        </is>
-      </c>
+      <c r="A84" s="22" t="n"/>
+      <c r="B84" s="0" t="n"/>
+      <c r="C84" s="0" t="n"/>
+      <c r="D84" s="0" t="n"/>
+      <c r="E84" s="0" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0.98304</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-4.008%</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>0.98233</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-4.0561%</t>
-        </is>
-      </c>
+      <c r="A85" s="22" t="n"/>
+      <c r="B85" s="0" t="n"/>
+      <c r="C85" s="0" t="n"/>
+      <c r="D85" s="0" t="n"/>
+      <c r="E85" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7793,13 +7603,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.1111111111111" customWidth="1" style="15" min="2" max="2"/>
-    <col width="14.4444444444444" customWidth="1" style="16" min="3" max="3"/>
-    <col width="13.3333333333333" customWidth="1" style="15" min="4" max="4"/>
-    <col width="16.2222222222222" customWidth="1" style="16" min="5" max="5"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.1083333333333" customWidth="1" style="16" min="2" max="2"/>
+    <col width="14.4416666666667" customWidth="1" style="17" min="3" max="3"/>
+    <col width="13.3333333333333" customWidth="1" style="16" min="4" max="4"/>
+    <col width="16.225" customWidth="1" style="17" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7808,7 +7618,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -7818,7 +7628,7 @@
           <t>回撤-有返息</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-无返息</t>
         </is>
@@ -7830,53 +7640,53 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>2025/03/18</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="n">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>2025/03/19</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="n">
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2025/03/20</t>
         </is>
@@ -7899,7 +7709,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2025/03/21</t>
         </is>
@@ -7912,7 +7722,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>1.00006</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -7922,7 +7732,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2025/03/24</t>
         </is>
@@ -7938,14 +7748,14 @@
       <c r="D6" s="0" t="n">
         <v>0.99893</v>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>-0.113%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2025/03/25</t>
         </is>
@@ -7968,7 +7778,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2025/03/26</t>
         </is>
@@ -7991,7 +7801,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2025/03/27</t>
         </is>
@@ -8014,7 +7824,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
@@ -8037,7 +7847,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>2025/03/31</t>
         </is>
@@ -8050,17 +7860,17 @@
           <t>-0.525%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.994701667</v>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>-0.5358%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
@@ -8073,17 +7883,17 @@
           <t>-0.502%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>0.994931667</v>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>-0.5128%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2025/04/02</t>
         </is>
@@ -8096,17 +7906,17 @@
           <t>-0.463%</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.995321667</v>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>-0.4738%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2025/04/03</t>
         </is>
@@ -8119,17 +7929,17 @@
           <t>-0.781%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.9921416669999999</v>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>-0.7918%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
@@ -8142,17 +7952,17 @@
           <t>-0.105%</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.998901667</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>-0.1158%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2025/04/08</t>
         </is>
@@ -8165,7 +7975,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>1.000771667</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -8175,7 +7985,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2025/04/09</t>
         </is>
@@ -8188,7 +7998,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>1.003401667</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -8198,7 +8008,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>2025/04/10</t>
         </is>
@@ -8211,7 +8021,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>1.003861667</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -8221,7 +8031,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2025/04/11</t>
         </is>
@@ -8234,7 +8044,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="20" t="n">
         <v>1.004091667</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -8244,7 +8054,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>2025/04/14</t>
         </is>
@@ -8257,17 +8067,17 @@
           <t>-0.0946%</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>1.003141667</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>-0.0946%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>2025/04/15</t>
         </is>
@@ -8280,17 +8090,17 @@
           <t>-0.3734%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>1.000341667</v>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>-0.3735%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>2025/04/16</t>
         </is>
@@ -8303,17 +8113,17 @@
           <t>-0.4551%</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <v>0.999521667</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>-0.4551%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>2025/04/17</t>
         </is>
@@ -8326,17 +8136,17 @@
           <t>-0.4242%</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
         <v>0.999831667</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>-0.4243%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
@@ -8349,17 +8159,17 @@
           <t>-0.3455%</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
         <v>1.000621667</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>-0.3456%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>2025/04/21</t>
         </is>
@@ -8372,17 +8182,17 @@
           <t>-0.2729%</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
         <v>1.001351667</v>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>-0.2729%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>2025/04/22</t>
         </is>
@@ -8395,17 +8205,17 @@
           <t>-0.1892%</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
         <v>1.002191667</v>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>-0.1892%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>2025/04/23</t>
         </is>
@@ -8418,17 +8228,17 @@
           <t>-0.2599%</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>1.001481667</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>-0.2599%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>2025/04/24</t>
         </is>
@@ -8441,17 +8251,17 @@
           <t>-0.0239%</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <v>1.003851667</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>-0.0239%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>2025/04/25</t>
         </is>
@@ -8464,7 +8274,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="20" t="n">
         <v>1.006051667</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -8474,7 +8284,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>2025/04/28</t>
         </is>
@@ -8487,17 +8297,17 @@
           <t>-0.0427%</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="16" t="n">
         <v>1.005621667</v>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>-0.0427%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>2025/04/29</t>
         </is>
@@ -8510,7 +8320,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="16" t="n">
         <v>1.006961667</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
@@ -8520,7 +8330,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
@@ -8533,7 +8343,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="16" t="n">
         <v>1.008141667</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
@@ -8543,7 +8353,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>2025/05/06</t>
         </is>
@@ -8556,7 +8366,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="20" t="n">
         <v>1.009121667</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
@@ -8566,7 +8376,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>2025/05/07</t>
         </is>
@@ -8579,17 +8389,17 @@
           <t>-0.1199%</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="16" t="n">
         <v>1.007911667</v>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>-0.1199%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>2025/05/08</t>
         </is>
@@ -8602,17 +8412,17 @@
           <t>-0.2338%</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
         <v>1.006761667</v>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>-0.2339%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>2025/05/09</t>
         </is>
@@ -8625,17 +8435,17 @@
           <t>-0.1367%</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>1.007741667</v>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>-0.1368%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>2025/05/12</t>
         </is>
@@ -8648,7 +8458,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>1.016081079</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
@@ -8658,7 +8468,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>2025/05/13</t>
         </is>
@@ -8671,7 +8481,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="16" t="n">
         <v>1.017002585</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
@@ -8681,7 +8491,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>2025/05/14</t>
         </is>
@@ -8694,7 +8504,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="20" t="n">
         <v>1.028102515</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
@@ -8704,7 +8514,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
@@ -8717,17 +8527,17 @@
           <t>-0.5679%</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="16" t="n">
         <v>1.022260992</v>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>-0.5682%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>2025/05/16</t>
         </is>
@@ -8740,17 +8550,17 @@
           <t>-1.1455%</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="16" t="n">
         <v>1.016256345</v>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>-1.1522%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
@@ -8763,17 +8573,17 @@
           <t>-1.1164%</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="16" t="n">
         <v>1.016556345</v>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>-1.1231%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>2025/05/20</t>
         </is>
@@ -8786,17 +8596,17 @@
           <t>-1.2233%</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="16" t="n">
         <v>1.015456345</v>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>-1.23%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>2025/05/21</t>
         </is>
@@ -8809,17 +8619,17 @@
           <t>-0.8733%</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="16" t="n">
         <v>1.019056345</v>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>-0.8799%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>2025/05/22</t>
         </is>
@@ -8832,17 +8642,17 @@
           <t>-1.3527%</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="16" t="n">
         <v>1.014126345</v>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>-1.3594%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>2025/05/23</t>
         </is>
@@ -8855,17 +8665,17 @@
           <t>-2.0081%</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="16" t="n">
         <v>1.007386345</v>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>-2.015%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>2025/05/26</t>
         </is>
@@ -8878,17 +8688,17 @@
           <t>-1.8506%</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
         <v>1.009006345</v>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>-1.8574%</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
@@ -8901,17 +8711,17 @@
           <t>-2.0538%</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="16" t="n">
         <v>1.006916345</v>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>-2.0607%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>2025/05/28</t>
         </is>
@@ -8924,17 +8734,17 @@
           <t>-2.1277%</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="16" t="n">
         <v>1.006155749</v>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>-2.1347%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>2025/05/29</t>
         </is>
@@ -8947,17 +8757,17 @@
           <t>-1.5462%</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="16" t="n">
         <v>1.012135749</v>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>-1.553%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>2025/05/30</t>
         </is>
@@ -8970,17 +8780,17 @@
           <t>-2.4486%</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="16" t="n">
         <v>1.002855749</v>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>-2.4557%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>2025/06/03</t>
         </is>
@@ -8993,17 +8803,17 @@
           <t>-2.753%</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="16" t="n">
         <v>0.999725749</v>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>-2.7601%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>2025/06/04</t>
         </is>
@@ -9016,17 +8826,17 @@
           <t>-3.0982%</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="16" t="n">
         <v>0.9961757490000001</v>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>-3.1054%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>2025/06/05</t>
         </is>
@@ -9039,17 +8849,17 @@
           <t>-3.1964%</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="16" t="n">
         <v>0.995165749</v>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>-3.2036%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>2025/06/06</t>
         </is>
@@ -9062,17 +8872,17 @@
           <t>-3.247%</t>
         </is>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D55" s="16" t="n">
         <v>0.994645749</v>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>-3.2542%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -9085,17 +8895,17 @@
           <t>-3.2801%</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
         <v>0.994270275</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>-3.2907%</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -9108,17 +8918,17 @@
           <t>-3.4901%</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
         <v>0.992068346</v>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>-3.5049%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -9131,17 +8941,17 @@
           <t>-3.1537%</t>
         </is>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D58" s="16" t="n">
         <v>0.995527209</v>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>-3.1685%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -9154,17 +8964,17 @@
           <t>-3.2013%</t>
         </is>
       </c>
-      <c r="D59" s="15" t="n">
+      <c r="D59" s="16" t="n">
         <v>0.995037117</v>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>-3.2162%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -9177,17 +8987,17 @@
           <t>-3.5543%</t>
         </is>
       </c>
-      <c r="D60" s="15" t="n">
+      <c r="D60" s="16" t="n">
         <v>0.991343972</v>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>-3.5754%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -9200,17 +9010,17 @@
           <t>-3.1702%</t>
         </is>
       </c>
-      <c r="D61" s="15" t="n">
+      <c r="D61" s="16" t="n">
         <v>0.995293972</v>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>-3.1912%</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -9223,17 +9033,17 @@
           <t>-3.0729%</t>
         </is>
       </c>
-      <c r="D62" s="15" t="n">
+      <c r="D62" s="16" t="n">
         <v>0.996293972</v>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>-3.0939%</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -9246,17 +9056,17 @@
           <t>-2.9776%</t>
         </is>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="16" t="n">
         <v>0.997273972</v>
       </c>
-      <c r="E63" s="16" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>-2.9986%</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -9269,17 +9079,17 @@
           <t>-3.4055%</t>
         </is>
       </c>
-      <c r="D64" s="15" t="n">
+      <c r="D64" s="16" t="n">
         <v>0.992873972</v>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>-3.4266%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -9292,17 +9102,17 @@
           <t>-3.4055%</t>
         </is>
       </c>
-      <c r="D65" s="15" t="n">
+      <c r="D65" s="16" t="n">
         <v>0.992873972</v>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>-3.4266%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -9315,17 +9125,17 @@
           <t>-3.5543%</t>
         </is>
       </c>
-      <c r="D66" s="15" t="n">
+      <c r="D66" s="16" t="n">
         <v>0.991343972</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>-3.5754%</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -9338,17 +9148,17 @@
           <t>-4.1096%</t>
         </is>
       </c>
-      <c r="D67" s="15" t="n">
+      <c r="D67" s="16" t="n">
         <v>0.985633972</v>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>-4.1308%</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -9361,17 +9171,17 @@
           <t>-4.2156%</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D68" s="16" t="n">
         <v>0.984539702</v>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>-4.2372%</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -9384,17 +9194,17 @@
           <t>-4.0872%</t>
         </is>
       </c>
-      <c r="D69" s="15" t="n">
+      <c r="D69" s="16" t="n">
         <v>0.9858597019999999</v>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>-4.1088%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -9407,17 +9217,17 @@
           <t>-4.0366%</t>
         </is>
       </c>
-      <c r="D70" s="15" t="n">
+      <c r="D70" s="16" t="n">
         <v>0.986379702</v>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>-4.0582%</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -9430,17 +9240,17 @@
           <t>-3.672%</t>
         </is>
       </c>
-      <c r="D71" s="15" t="n">
+      <c r="D71" s="16" t="n">
         <v>0.987090281</v>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>-3.9891%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -9453,17 +9263,17 @@
           <t>-3.8538%</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
+      <c r="D72" s="16" t="n">
         <v>0.985220281</v>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>-4.171%</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -9476,17 +9286,17 @@
           <t>-4.5141%</t>
         </is>
       </c>
-      <c r="D73" s="15" t="n">
+      <c r="D73" s="16" t="n">
         <v>0.978430281</v>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>-4.8314%</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -9499,17 +9309,17 @@
           <t>-4.4062%</t>
         </is>
       </c>
-      <c r="D74" s="15" t="n">
+      <c r="D74" s="16" t="n">
         <v>0.979540281</v>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>-4.7235%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -9522,17 +9332,17 @@
           <t>-4.343%</t>
         </is>
       </c>
-      <c r="D75" s="15" t="n">
+      <c r="D75" s="16" t="n">
         <v>0.9801902810000001</v>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>-4.6603%</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="20" t="inlineStr">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9542,7 +9352,7 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>-2.4268%</t>
+          <t>-2.4484%</t>
         </is>
       </c>
       <c r="D76" s="0" t="n">
@@ -9550,12 +9360,12 @@
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>-2.5176%</t>
+          <t>-2.496%</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+      <c r="A77" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9578,7 +9388,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+      <c r="A78" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9601,7 +9411,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9624,7 +9434,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="20" t="inlineStr">
+      <c r="A80" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9647,7 +9457,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="inlineStr">
+      <c r="A81" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -9670,96 +9480,32 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D82" s="0" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E82" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
+      <c r="A82" s="22" t="n"/>
+      <c r="B82" s="0" t="n"/>
+      <c r="C82" s="0" t="n"/>
+      <c r="D82" s="0" t="n"/>
+      <c r="E82" s="0" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C83" s="0" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D83" s="0" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E83" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
+      <c r="A83" s="22" t="n"/>
+      <c r="B83" s="0" t="n"/>
+      <c r="C83" s="0" t="n"/>
+      <c r="D83" s="0" t="n"/>
+      <c r="E83" s="0" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C84" s="0" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D84" s="0" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E84" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
+      <c r="A84" s="22" t="n"/>
+      <c r="B84" s="0" t="n"/>
+      <c r="C84" s="0" t="n"/>
+      <c r="D84" s="0" t="n"/>
+      <c r="E84" s="0" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
+      <c r="A85" s="22" t="n"/>
+      <c r="B85" s="0" t="n"/>
+      <c r="C85" s="0" t="n"/>
+      <c r="D85" s="0" t="n"/>
+      <c r="E85" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9774,13 +9520,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="14.6666666666667" customWidth="1" style="15" min="2" max="2"/>
-    <col width="16.6666666666667" customWidth="1" style="16" min="3" max="3"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="4" max="4"/>
-    <col width="16.8888888888889" customWidth="1" style="1" min="5" max="5"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="14.6666666666667" customWidth="1" style="16" min="2" max="2"/>
+    <col width="16.6666666666667" customWidth="1" style="17" min="3" max="3"/>
+    <col width="13.5583333333333" customWidth="1" style="1" min="4" max="4"/>
+    <col width="16.8916666666667" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9789,7 +9535,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -9799,7 +9545,7 @@
           <t>回撤-有返息</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-无返息</t>
         </is>
@@ -9811,7 +9557,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -9819,7 +9565,7 @@
       <c r="B2" s="0" t="n">
         <v>0.99988</v>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>-0.0124%</t>
         </is>
@@ -9827,14 +9573,14 @@
       <c r="D2" s="0" t="n">
         <v>0.99988</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>-0.0124%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -9857,7 +9603,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -9880,7 +9626,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -9903,7 +9649,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -9926,7 +9672,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -9939,7 +9685,7 @@
           <t>-0.4362%</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>1.000064696</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -9949,7 +9695,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -9962,7 +9708,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>1.000114696</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -9972,7 +9718,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -9985,7 +9731,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>1.000334696</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -9995,7 +9741,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -10008,7 +9754,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>1.000374696</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -10018,7 +9764,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -10031,7 +9777,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>1.000554696</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -10041,7 +9787,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -10054,7 +9800,7 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>1.000684696</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -10064,7 +9810,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -10077,17 +9823,17 @@
           <t>-0.4798%</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.998564696</v>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>-0.5028%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -10100,17 +9846,17 @@
           <t>-0.3397%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.997284696</v>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>-0.3398%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -10123,17 +9869,17 @@
           <t>-0.3357%</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.997324696</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>-0.3358%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -10146,17 +9892,17 @@
           <t>-0.3207%</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.997474696</v>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>-0.3208%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -10169,17 +9915,17 @@
           <t>-0.4317%</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.996364696</v>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>-0.4317%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -10192,17 +9938,17 @@
           <t>-0.4157%</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.996524696</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>-0.4157%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -10215,17 +9961,17 @@
           <t>-0.3987%</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>0.996694696</v>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>-0.3987%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -10238,17 +9984,17 @@
           <t>-0.3927%</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>0.996754696</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>-0.3927%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -10261,17 +10007,17 @@
           <t>-0.3887%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>0.996794696</v>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>-0.3887%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -10281,7 +10027,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>-0.4798%</t>
+          <t>-0.4913%</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
@@ -10289,12 +10035,12 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>-0.6978%</t>
+          <t>-0.6863%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -10317,7 +10063,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -10340,7 +10086,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -10363,7 +10109,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -10386,7 +10132,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -10409,96 +10155,32 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>0.99588</v>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>-0.4913%</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0.99382</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>-0.6863%</t>
-        </is>
-      </c>
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="0" t="n"/>
+      <c r="C28" s="0" t="n"/>
+      <c r="D28" s="0" t="n"/>
+      <c r="E28" s="0" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>0.99588</v>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>-0.4913%</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>0.99382</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>-0.6863%</t>
-        </is>
-      </c>
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="0" t="n"/>
+      <c r="C29" s="0" t="n"/>
+      <c r="D29" s="0" t="n"/>
+      <c r="E29" s="0" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>0.99588</v>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>-0.4913%</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>0.99382</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>-0.6863%</t>
-        </is>
-      </c>
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="0" t="n"/>
+      <c r="C30" s="0" t="n"/>
+      <c r="D30" s="0" t="n"/>
+      <c r="E30" s="0" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.99588</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-0.4913%</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.99382</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-0.6863%</t>
-        </is>
-      </c>
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="0" t="n"/>
+      <c r="C31" s="0" t="n"/>
+      <c r="D31" s="0" t="n"/>
+      <c r="E31" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10512,14 +10194,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.2222222222222" customWidth="1" style="15" min="2" max="2"/>
-    <col width="13.2222222222222" customWidth="1" style="16" min="3" max="3"/>
-    <col width="16.3333333333333" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15.2222222222222" customWidth="1" style="16" min="5" max="5"/>
-    <col width="13.2222222222222" customWidth="1" style="1" min="6" max="6"/>
+    <col width="11.6333333333333" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15.225" customWidth="1" style="16" min="2" max="2"/>
+    <col width="13.225" customWidth="1" style="17" min="3" max="3"/>
+    <col width="16.3333333333333" customWidth="1" style="16" min="4" max="4"/>
+    <col width="15.225" customWidth="1" style="17" min="5" max="5"/>
+    <col width="13.225" customWidth="1" style="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10528,7 +10210,7 @@
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-有返息</t>
         </is>
@@ -10538,7 +10220,7 @@
           <t>回撤-有返息</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"> 净值-无返息</t>
         </is>
@@ -10550,7 +10232,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>2025/06/09</t>
         </is>
@@ -10558,7 +10240,7 @@
       <c r="B2" s="0" t="n">
         <v>0.99988</v>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>-0.0124%</t>
         </is>
@@ -10566,14 +10248,14 @@
       <c r="D2" s="0" t="n">
         <v>0.99988</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>-0.0124%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>2025/06/10</t>
         </is>
@@ -10589,14 +10271,14 @@
       <c r="D3" s="0" t="n">
         <v>1.00005</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2025/06/11</t>
         </is>
@@ -10612,14 +10294,14 @@
       <c r="D4" s="0" t="n">
         <v>1.0001</v>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2025/06/12</t>
         </is>
@@ -10635,14 +10317,14 @@
       <c r="D5" s="0" t="n">
         <v>1.00013</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2025/06/13</t>
         </is>
@@ -10658,14 +10340,14 @@
       <c r="D6" s="0" t="n">
         <v>1.00024</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2025/06/16</t>
         </is>
@@ -10678,17 +10360,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>1.000184696</v>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2025/06/17</t>
         </is>
@@ -10701,17 +10383,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>1.000224696</v>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2025/06/18</t>
         </is>
@@ -10724,17 +10406,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>1.000334696</v>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>2025/06/19</t>
         </is>
@@ -10747,17 +10429,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>1.000374696</v>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>2025/06/20</t>
         </is>
@@ -10770,17 +10452,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>1.000554696</v>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
@@ -10793,17 +10475,17 @@
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>1.000684696</v>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2025/06/24</t>
         </is>
@@ -10816,17 +10498,17 @@
           <t>-0.2118%</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.998564696</v>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>-0.2119%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
@@ -10839,17 +10521,17 @@
           <t>-0.3397%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.997284696</v>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>-0.3398%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2025/06/26</t>
         </is>
@@ -10862,17 +10544,17 @@
           <t>-0.3357%</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.997324696</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>-0.3358%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>2025/06/27</t>
         </is>
@@ -10885,17 +10567,17 @@
           <t>-0.3207%</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.997474696</v>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>-0.3208%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
@@ -10908,17 +10590,17 @@
           <t>-0.4317%</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>0.996364696</v>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>-0.4317%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>2025/07/01</t>
         </is>
@@ -10931,17 +10613,17 @@
           <t>-0.4157%</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>0.996524696</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>-0.4157%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
@@ -10954,17 +10636,17 @@
           <t>-0.3987%</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>0.996694696</v>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>-0.3987%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
@@ -10977,17 +10659,17 @@
           <t>-0.3927%</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>0.996754696</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>-0.3927%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>2025/07/04</t>
         </is>
@@ -11000,17 +10682,17 @@
           <t>-0.3887%</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>0.996794696</v>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>-0.3887%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -11020,7 +10702,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>-0.0618%</t>
+          <t>-0.0733%</t>
         </is>
       </c>
       <c r="D22" s="0" t="n">
@@ -11028,12 +10710,12 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>-0.2798%</t>
+          <t>-0.2683%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -11056,7 +10738,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -11079,7 +10761,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -11102,7 +10784,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -11125,7 +10807,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>2025/07/07</t>
         </is>
@@ -11148,96 +10830,32 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>1.00007</v>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>-0.0733%</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>-0.2683%</t>
-        </is>
-      </c>
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="0" t="n"/>
+      <c r="C28" s="0" t="n"/>
+      <c r="D28" s="0" t="n"/>
+      <c r="E28" s="0" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>1.00007</v>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>-0.0733%</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>-0.2683%</t>
-        </is>
-      </c>
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="0" t="n"/>
+      <c r="C29" s="0" t="n"/>
+      <c r="D29" s="0" t="n"/>
+      <c r="E29" s="0" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>1.00007</v>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>-0.0733%</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>-0.2683%</t>
-        </is>
-      </c>
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="0" t="n"/>
+      <c r="C30" s="0" t="n"/>
+      <c r="D30" s="0" t="n"/>
+      <c r="E30" s="0" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1.00007</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-0.0733%</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-0.2683%</t>
-        </is>
-      </c>
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="0" t="n"/>
+      <c r="C31" s="0" t="n"/>
+      <c r="D31" s="0" t="n"/>
+      <c r="E31" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
